--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_12.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03412493165635778</v>
+        <v>0.03002585925202282</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008479572374271745</v>
+        <v>0.008472774029021725</v>
       </c>
       <c r="C2" t="n">
-        <v>75555324</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>75555324</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>50084990</v>
+        <v>4039320</v>
       </c>
       <c r="L2" t="n">
-        <v>25185118</v>
+        <v>1538215</v>
       </c>
       <c r="M2" t="n">
-        <v>5645675</v>
+        <v>276538</v>
       </c>
       <c r="N2" t="n">
-        <v>213729</v>
+        <v>4728</v>
       </c>
       <c r="O2" t="n">
-        <v>3365361</v>
+        <v>156598</v>
       </c>
       <c r="P2" t="n">
-        <v>1168327</v>
+        <v>144</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999765157699585</v>
+        <v>0.9999915957450867</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8008208870887756</v>
+        <v>0.6955493092536926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6481192708015442</v>
+        <v>0.5237749814987183</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5549849271774292</v>
+        <v>0.3757703006267548</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1735635995864868</v>
+        <v>0.03753334283828735</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6061331629753113</v>
+        <v>0.3819938600063324</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7673216462135315</v>
+        <v>0.2562277615070343</v>
       </c>
       <c r="X2" t="n">
-        <v>75555324</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>75555324</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>57174686</v>
+        <v>4717265</v>
       </c>
       <c r="AG2" t="n">
-        <v>35855196</v>
+        <v>3042463</v>
       </c>
       <c r="AH2" t="n">
-        <v>9629982</v>
+        <v>809406</v>
       </c>
       <c r="AI2" t="n">
-        <v>708871</v>
+        <v>59391</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5520941</v>
+        <v>462109</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9555858373641968</v>
+        <v>0.9541478753089905</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9119958281517029</v>
+        <v>0.9129630327224731</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.858262836933136</v>
+        <v>0.8576433062553406</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6616336703300476</v>
+        <v>0.6601934432983398</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019981026649475</v>
+        <v>0.9016708135604858</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.009170564383596688</v>
+        <v>0.007916065678604766</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002033221905254034</v>
+        <v>0.002031055628665047</v>
       </c>
       <c r="C3" t="n">
-        <v>1117</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>50084990</v>
+        <v>4039320</v>
       </c>
       <c r="E3" t="n">
-        <v>9197072</v>
+        <v>837411</v>
       </c>
       <c r="F3" t="n">
-        <v>365447</v>
+        <v>43442</v>
       </c>
       <c r="G3" t="n">
-        <v>32351</v>
+        <v>3877</v>
       </c>
       <c r="H3" t="n">
-        <v>29480</v>
+        <v>4419</v>
       </c>
       <c r="I3" t="n">
-        <v>1264</v>
+        <v>32</v>
       </c>
       <c r="J3" t="n">
-        <v>119879700</v>
+        <v>10016569</v>
       </c>
       <c r="K3" t="n">
-        <v>123268006</v>
+        <v>9633029</v>
       </c>
       <c r="L3" t="n">
-        <v>142349547</v>
+        <v>11585561</v>
       </c>
       <c r="M3" t="n">
-        <v>179674086</v>
+        <v>14924684</v>
       </c>
       <c r="N3" t="n">
-        <v>193346555</v>
+        <v>16118291</v>
       </c>
       <c r="O3" t="n">
-        <v>187124702</v>
+        <v>15563255</v>
       </c>
       <c r="P3" t="n">
-        <v>192759928</v>
+        <v>16135132</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8387798666954041</v>
+        <v>0.8195824027061462</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6389956474304199</v>
+        <v>0.4597906768321991</v>
       </c>
       <c r="T3" t="n">
-        <v>0.502475380897522</v>
+        <v>0.2924684584140778</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1992703378200531</v>
+        <v>0.05249308794736862</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5494217276573181</v>
+        <v>0.3052628338336945</v>
       </c>
       <c r="W3" t="n">
-        <v>0.50302654504776</v>
+        <v>0.0007420767797157168</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57174686</v>
+        <v>4717265</v>
       </c>
       <c r="Z3" t="n">
-        <v>2353555</v>
+        <v>195844</v>
       </c>
       <c r="AA3" t="n">
-        <v>101352</v>
+        <v>8538</v>
       </c>
       <c r="AB3" t="n">
-        <v>81500</v>
+        <v>6822</v>
       </c>
       <c r="AC3" t="n">
-        <v>268</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>119881476</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>133067688</v>
+        <v>11174399</v>
       </c>
       <c r="AG3" t="n">
-        <v>152563309</v>
+        <v>12694080</v>
       </c>
       <c r="AH3" t="n">
-        <v>182610739</v>
+        <v>15249719</v>
       </c>
       <c r="AI3" t="n">
-        <v>194001718</v>
+        <v>16208962</v>
       </c>
       <c r="AJ3" t="n">
-        <v>188711673</v>
+        <v>15766212</v>
       </c>
       <c r="AK3" t="n">
-        <v>192955027</v>
+        <v>16122228</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575119614601135</v>
+        <v>0.9571381807327271</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097163677215576</v>
+        <v>0.9094282388687134</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570859432220459</v>
+        <v>0.8560332655906677</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.660916268825531</v>
+        <v>0.6593944430351257</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.901337206363678</v>
+        <v>0.900807797908783</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.07393202109851134</v>
+        <v>0.06649413367842551</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03205179288635735</v>
+        <v>0.03202893469858889</v>
       </c>
       <c r="C4" t="n">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11351725</v>
+        <v>1556794</v>
       </c>
       <c r="E4" t="n">
-        <v>25185118</v>
+        <v>1538215</v>
       </c>
       <c r="F4" t="n">
-        <v>2388137</v>
+        <v>196819</v>
       </c>
       <c r="G4" t="n">
-        <v>162483</v>
+        <v>19105</v>
       </c>
       <c r="H4" t="n">
-        <v>303635</v>
+        <v>34460</v>
       </c>
       <c r="I4" t="n">
-        <v>22354</v>
+        <v>64</v>
       </c>
       <c r="J4" t="n">
-        <v>1776</v>
+        <v>53</v>
       </c>
       <c r="K4" t="n">
-        <v>12457073</v>
+        <v>1768061</v>
       </c>
       <c r="L4" t="n">
-        <v>13673654</v>
+        <v>1398571</v>
       </c>
       <c r="M4" t="n">
-        <v>4526989</v>
+        <v>459385</v>
       </c>
       <c r="N4" t="n">
-        <v>1017687</v>
+        <v>121240</v>
       </c>
       <c r="O4" t="n">
-        <v>2186820</v>
+        <v>253351</v>
       </c>
       <c r="P4" t="n">
-        <v>354277</v>
+        <v>418</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999882578849792</v>
+        <v>0.9999957680702209</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8193610310554504</v>
+        <v>0.7524889707565308</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6435251235961914</v>
+        <v>0.4897016286849976</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5274264216423035</v>
+        <v>0.328927218914032</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1855307221412659</v>
+        <v>0.04377027973532677</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5763858556747437</v>
+        <v>0.3393449187278748</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6076809167861938</v>
+        <v>0.001479867612943053</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2482224</v>
+        <v>211876</v>
       </c>
       <c r="Z4" t="n">
-        <v>35855196</v>
+        <v>3042463</v>
       </c>
       <c r="AA4" t="n">
-        <v>995139</v>
+        <v>84107</v>
       </c>
       <c r="AB4" t="n">
-        <v>66452</v>
+        <v>5676</v>
       </c>
       <c r="AC4" t="n">
-        <v>13767</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2657391</v>
+        <v>226691</v>
       </c>
       <c r="AG4" t="n">
-        <v>3459892</v>
+        <v>290052</v>
       </c>
       <c r="AH4" t="n">
-        <v>1590336</v>
+        <v>134350</v>
       </c>
       <c r="AI4" t="n">
-        <v>362524</v>
+        <v>30569</v>
       </c>
       <c r="AJ4" t="n">
-        <v>599849</v>
+        <v>50394</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9565479159355164</v>
+        <v>0.9556406140327454</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9108546376228333</v>
+        <v>0.9111921787261963</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576740026473999</v>
+        <v>0.8568375706672668</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.661274790763855</v>
+        <v>0.6597936749458313</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016675353050232</v>
+        <v>0.9012390971183777</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>113</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>796731</v>
+        <v>154763</v>
       </c>
       <c r="E5" t="n">
-        <v>3511752</v>
+        <v>406347</v>
       </c>
       <c r="F5" t="n">
-        <v>5645675</v>
+        <v>276538</v>
       </c>
       <c r="G5" t="n">
-        <v>316532</v>
+        <v>31389</v>
       </c>
       <c r="H5" t="n">
-        <v>887388</v>
+        <v>76400</v>
       </c>
       <c r="I5" t="n">
-        <v>77534</v>
+        <v>89</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9626731</v>
+        <v>889190</v>
       </c>
       <c r="L5" t="n">
-        <v>14228481</v>
+        <v>1807253</v>
       </c>
       <c r="M5" t="n">
-        <v>5590050</v>
+        <v>668993</v>
       </c>
       <c r="N5" t="n">
-        <v>858829</v>
+        <v>85341</v>
       </c>
       <c r="O5" t="n">
-        <v>2759917</v>
+        <v>356396</v>
       </c>
       <c r="P5" t="n">
-        <v>1154268</v>
+        <v>193906</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999909400939941</v>
+        <v>0.9999967813491821</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8870028257369995</v>
+        <v>0.8372739553451538</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8572319149971008</v>
+        <v>0.8036801815032959</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9482337236404419</v>
+        <v>0.9308998584747314</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9903983473777771</v>
+        <v>0.987349271774292</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9746888279914856</v>
+        <v>0.962660014629364</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9922811388969421</v>
+        <v>0.9880998730659485</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>96476</v>
+        <v>8160</v>
       </c>
       <c r="Z5" t="n">
-        <v>1031511</v>
+        <v>87923</v>
       </c>
       <c r="AA5" t="n">
-        <v>9629982</v>
+        <v>809406</v>
       </c>
       <c r="AB5" t="n">
-        <v>119780</v>
+        <v>10057</v>
       </c>
       <c r="AC5" t="n">
-        <v>350372</v>
+        <v>29344</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2537035</v>
+        <v>211245</v>
       </c>
       <c r="AG5" t="n">
-        <v>3558403</v>
+        <v>303005</v>
       </c>
       <c r="AH5" t="n">
-        <v>1605743</v>
+        <v>136125</v>
       </c>
       <c r="AI5" t="n">
-        <v>363687</v>
+        <v>30678</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604337</v>
+        <v>50885</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734214544296265</v>
+        <v>0.9731814861297607</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9640891551971436</v>
+        <v>0.9636821150779724</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836465120315552</v>
+        <v>0.9834365248680115</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962841868400574</v>
+        <v>0.9962493181228638</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938384890556335</v>
+        <v>0.9937978386878967</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983670115470886</v>
+        <v>0.9983611106872559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>199689</v>
+        <v>26538</v>
       </c>
       <c r="E6" t="n">
-        <v>257732</v>
+        <v>26985</v>
       </c>
       <c r="F6" t="n">
-        <v>272260</v>
+        <v>23962</v>
       </c>
       <c r="G6" t="n">
-        <v>213729</v>
+        <v>4728</v>
       </c>
       <c r="H6" t="n">
-        <v>117908</v>
+        <v>7795</v>
       </c>
       <c r="I6" t="n">
-        <v>11127</v>
+        <v>54</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78160</v>
+        <v>6619</v>
       </c>
       <c r="Z6" t="n">
-        <v>64136</v>
+        <v>5393</v>
       </c>
       <c r="AA6" t="n">
-        <v>131652</v>
+        <v>11143</v>
       </c>
       <c r="AB6" t="n">
-        <v>708871</v>
+        <v>59391</v>
       </c>
       <c r="AC6" t="n">
-        <v>83961</v>
+        <v>7037</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>99827</v>
+        <v>26811</v>
       </c>
       <c r="E7" t="n">
-        <v>638107</v>
+        <v>113651</v>
       </c>
       <c r="F7" t="n">
-        <v>1348280</v>
+        <v>163799</v>
       </c>
       <c r="G7" t="n">
-        <v>431599</v>
+        <v>51948</v>
       </c>
       <c r="H7" t="n">
-        <v>3365361</v>
+        <v>156598</v>
       </c>
       <c r="I7" t="n">
-        <v>241998</v>
+        <v>179</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>195</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9717</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358212</v>
+        <v>30228</v>
       </c>
       <c r="AB7" t="n">
-        <v>91598</v>
+        <v>7747</v>
       </c>
       <c r="AC7" t="n">
-        <v>5520941</v>
+        <v>462109</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>9101</v>
+        <v>3155</v>
       </c>
       <c r="E8" t="n">
-        <v>68991</v>
+        <v>14177</v>
       </c>
       <c r="F8" t="n">
-        <v>152865</v>
+        <v>31363</v>
       </c>
       <c r="G8" t="n">
-        <v>74722</v>
+        <v>14921</v>
       </c>
       <c r="H8" t="n">
-        <v>848409</v>
+        <v>130277</v>
       </c>
       <c r="I8" t="n">
-        <v>1168327</v>
+        <v>144</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
